--- a/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.001</v>
+        <v>0.059</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.096</v>
+        <v>-0.095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.076</v>
+        <v>0.091</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.059</v>
+        <v>0.033</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02</v>
+        <v>0.026</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03899999999999999</v>
+        <v>0.007000000000000003</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.007</v>
+        <v>-0.012</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.021</v>
+        <v>0.003</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.014</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.033</v>
+        <v>-0.054</v>
       </c>
       <c r="D10" t="n">
-        <v>0.026</v>
+        <v>-0.024</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007000000000000003</v>
+        <v>0.03</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="D12" t="n">
-        <v>0.018</v>
+        <v>-0.003</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.003999999999999998</v>
+        <v>0.004</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.044</v>
+        <v>0.185</v>
       </c>
       <c r="D13" t="n">
-        <v>0.027</v>
+        <v>0.011</v>
       </c>
       <c r="E13" t="n">
-        <v>0.017</v>
+        <v>0.174</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.181</v>
+        <v>-0.007</v>
       </c>
       <c r="D14" t="n">
-        <v>0.012</v>
+        <v>-0.021</v>
       </c>
       <c r="E14" t="n">
-        <v>0.169</v>
+        <v>-0.014</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.076</v>
+        <v>-0.09</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.002</v>
+        <v>-0.031</v>
       </c>
       <c r="E15" t="n">
-        <v>0.074</v>
+        <v>0.059</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="D16" t="n">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="E16" t="n">
-        <v>0.006</v>
+        <v>-0.003999999999999998</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.008</v>
+        <v>-0.096</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.011</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.012</v>
+        <v>0.036</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.034</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.054</v>
+        <v>-0.008</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.024</v>
+        <v>-0.011</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.185</v>
+        <v>0.076</v>
       </c>
       <c r="D21" t="n">
-        <v>0.011</v>
+        <v>-0.002</v>
       </c>
       <c r="E21" t="n">
-        <v>0.174</v>
+        <v>0.074</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.215</v>
+        <v>0.075</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.058</v>
+        <v>0.005</v>
       </c>
       <c r="E22" t="n">
-        <v>0.157</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.095</v>
+        <v>0.044</v>
       </c>
       <c r="D24" t="n">
-        <v>0.004</v>
+        <v>0.027</v>
       </c>
       <c r="E24" t="n">
-        <v>0.091</v>
+        <v>0.017</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.036</v>
+        <v>-0.015</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.002</v>
+        <v>-0.034</v>
       </c>
       <c r="E26" t="n">
-        <v>0.034</v>
+        <v>-0.019</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.075</v>
+        <v>-0.181</v>
       </c>
       <c r="D27" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.169</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.392</v>
+        <v>-0.215</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.03</v>
+        <v>-0.058</v>
       </c>
       <c r="E29" t="n">
-        <v>0.362</v>
+        <v>0.157</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.015</v>
+        <v>-0.001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.034</v>
+        <v>-0.002</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.019</v>
+        <v>-0.001</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.09</v>
+        <v>-0.392</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.031</v>
+        <v>-0.03</v>
       </c>
       <c r="E32" t="n">
-        <v>0.059</v>
+        <v>0.362</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1397,7 +1397,7 @@
         <v>0.1622858171513956</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858932286536427</v>
+        <v>1.858932286536428</v>
       </c>
       <c r="F2" t="n">
         <v>1.152192362074074</v>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.353573802712667</v>
+        <v>1.353573802712666</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1117816230435669</v>
+        <v>0.1117816230435639</v>
       </c>
       <c r="D2" t="n">
-        <v>1.134485847413843</v>
+        <v>1.134485847413849</v>
       </c>
       <c r="E2" t="n">
-        <v>1.572661758011491</v>
+        <v>1.572661758011484</v>
       </c>
       <c r="F2" t="n">
-        <v>9.4536435497379e-34</v>
+        <v>9.453643549700572e-34</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01684973934795499</v>
+        <v>0.01684973934795501</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02218339938737486</v>
+        <v>0.02218339938737487</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02662892450596764</v>
+        <v>-0.02662892450596763</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06032840320187763</v>
+        <v>0.06032840320187766</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4475144961087134</v>
+        <v>0.4475144961087129</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004680048186736493</v>
+        <v>0.004680048186736469</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05214567125446188</v>
+        <v>0.05214567125446187</v>
       </c>
       <c r="D4" t="n">
         <v>-0.09752358942167437</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1068836857951474</v>
+        <v>0.1068836857951473</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9284862752865162</v>
+        <v>0.9284862752865165</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01802753319671225</v>
+        <v>-0.01802753319671224</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03510599180500087</v>
+        <v>0.03510599180500089</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08683401277607224</v>
+        <v>-0.08683401277607226</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05077894638264772</v>
+        <v>0.05077894638264778</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6075895309376501</v>
+        <v>0.6075895309376507</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.047511486473317</v>
+        <v>0.04751148647331688</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03543442571134347</v>
+        <v>0.03543442571134346</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.02193871173377628</v>
+        <v>-0.02193871173377639</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1169616846804103</v>
+        <v>0.1169616846804101</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1799761535400176</v>
+        <v>0.1799761535400188</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.02470344421341207</v>
+        <v>-0.02470344421341204</v>
       </c>
       <c r="C7" t="n">
         <v>0.03375913660148892</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09087013610149827</v>
+        <v>-0.09087013610149824</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04146324767467413</v>
+        <v>0.04146324767467416</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4643176277928891</v>
+        <v>0.4643176277928895</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01925751157934899</v>
+        <v>0.01925751157934903</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03249460700462259</v>
+        <v>0.03249460700462257</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04443074784149426</v>
+        <v>-0.04443074784149418</v>
       </c>
       <c r="E8" t="n">
         <v>0.08294577100019224</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5534240052549222</v>
+        <v>0.5534240052549212</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1080064052043351</v>
+        <v>0.1080064052043349</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05860207996072136</v>
+        <v>0.05860207996072135</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.006851560937815207</v>
+        <v>-0.006851560937815346</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2228643713464854</v>
+        <v>0.2228643713464852</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06532210486217095</v>
+        <v>0.06532210486217126</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.002155543931905708</v>
+        <v>-0.002155543931905756</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06002430441707508</v>
+        <v>0.06002430441707522</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1198010187864413</v>
+        <v>-0.1198010187864417</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1154899309226299</v>
+        <v>0.1154899309226301</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9713531768625306</v>
+        <v>0.9713531768625301</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1382027330165259</v>
+        <v>0.1382027330165258</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05978746914895725</v>
+        <v>0.0597874691489572</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0210214467577701</v>
+        <v>0.02102144675777011</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2553840192752816</v>
+        <v>0.2553840192752815</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02080156404096282</v>
+        <v>0.0208015640409628</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1224061847775766</v>
+        <v>0.1224061847775765</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05763612293239083</v>
+        <v>0.05763612293239091</v>
       </c>
       <c r="D13" t="n">
-        <v>0.009441459621567491</v>
+        <v>0.009441459621567241</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2353709099335857</v>
+        <v>0.2353709099335858</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03368892209436403</v>
+        <v>0.03368892209436439</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.01605948332440313</v>
+        <v>-0.01605948332440322</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05643770073365858</v>
+        <v>0.05643770073365874</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1266753441326237</v>
+        <v>-0.1266753441326241</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09455637748381747</v>
+        <v>0.09455637748381769</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7759870816563202</v>
+        <v>0.7759870816563196</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1035989698740269</v>
+        <v>0.1035989698740268</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06028797128686283</v>
+        <v>0.06028797128686304</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.01456328254920913</v>
+        <v>-0.01456328254920962</v>
       </c>
       <c r="E15" t="n">
-        <v>0.221761222297263</v>
+        <v>0.2217612222972633</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08572331750029738</v>
+        <v>0.08572331750029868</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02083305428097073</v>
+        <v>0.02083305428097069</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05652379902083965</v>
+        <v>0.05652379902083966</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.08995155606925535</v>
+        <v>-0.08995155606925542</v>
       </c>
       <c r="E16" t="n">
         <v>0.1316176646311968</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7124472356899141</v>
+        <v>0.7124472356899145</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08702475870816762</v>
+        <v>0.08702475870816749</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05638348369484429</v>
+        <v>0.05638348369484424</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02348483865662856</v>
+        <v>-0.02348483865662861</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1975343560729638</v>
+        <v>0.1975343560729636</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1227230457706392</v>
+        <v>0.1227230457706394</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.04234015284045975</v>
+        <v>0.04234015284045958</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05979849830098834</v>
+        <v>0.05979849830098842</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.07486275015905701</v>
+        <v>-0.07486275015905733</v>
       </c>
       <c r="E18" t="n">
         <v>0.1595430558399765</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4789160136810096</v>
+        <v>0.478916013681012</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06739003077305372</v>
+        <v>0.06739003077305362</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05810774114365006</v>
+        <v>0.05810774114365014</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.04649904909147669</v>
+        <v>-0.04649904909147695</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1812791106375841</v>
+        <v>0.1812791106375842</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2461535643763861</v>
+        <v>0.2461535643763876</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.001531808616490247</v>
+        <v>-0.001531808616490342</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0561772097506834</v>
+        <v>0.05617720975068342</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1116371164797821</v>
+        <v>-0.1116371164797822</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1085734992468016</v>
+        <v>0.1085734992468015</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9782464274556042</v>
+        <v>0.9782464274556028</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09669367936441987</v>
+        <v>0.0966936793644198</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05914172983936312</v>
+        <v>0.05914172983936319</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.01922198110412968</v>
+        <v>-0.0192219811041299</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2126093398329694</v>
+        <v>0.2126093398329695</v>
       </c>
       <c r="F21" t="n">
-        <v>0.102059855175029</v>
+        <v>0.1020598551750296</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04161731869983509</v>
+        <v>0.04161731869983511</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05891200060017088</v>
+        <v>0.05891200060017087</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07384808073370189</v>
+        <v>-0.07384808073370185</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1570827181333721</v>
+        <v>0.157082718133372</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4799195657238089</v>
+        <v>0.4799195657238088</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.08357026518461759</v>
+        <v>0.08357026518461746</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05655202274398946</v>
+        <v>0.0565520227439895</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.02726966264649175</v>
+        <v>-0.02726966264649196</v>
       </c>
       <c r="E23" t="n">
         <v>0.1944101930157269</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1394722742661425</v>
+        <v>0.1394722742661434</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.06180044074249919</v>
+        <v>-0.06180044074249923</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05009160278186423</v>
+        <v>0.05009160278186418</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1599781781228395</v>
+        <v>-0.1599781781228394</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03637729663784108</v>
+        <v>0.03637729663784095</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2172966281742635</v>
+        <v>0.2172966281742628</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.009821945543911244</v>
+        <v>0.009821945543911225</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0279199029012004</v>
+        <v>0.02791990290120031</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04490005859429691</v>
+        <v>-0.04490005859429675</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06454394968211939</v>
+        <v>0.0645439496821192</v>
       </c>
       <c r="F25" t="n">
-        <v>0.724995680679504</v>
+        <v>0.7249956806795036</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.007141328148583884</v>
+        <v>0.007141328148584141</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03367730708489815</v>
+        <v>0.03367730708489822</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0588649808341121</v>
+        <v>-0.05886498083411196</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07314763713127986</v>
+        <v>0.07314763713128025</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8320667485145421</v>
+        <v>0.8320667485145364</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04372637637293084</v>
+        <v>-0.04372637637293077</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03548652400230915</v>
+        <v>0.03548652400230919</v>
       </c>
       <c r="D27" t="n">
         <v>-0.113278685353973</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02582593260811128</v>
+        <v>0.02582593260811141</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2178756304376083</v>
+        <v>0.2178756304376095</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05468422483154237</v>
+        <v>-0.05468422483154227</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03444153292457984</v>
+        <v>0.03444153292457987</v>
       </c>
       <c r="D28" t="n">
         <v>-0.1221883889360693</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01281993927298459</v>
+        <v>0.01281993927298476</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1123449775185344</v>
+        <v>0.1123449775185354</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02089734168100155</v>
+        <v>-0.02089734168100148</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03306200599683337</v>
+        <v>0.03306200599683339</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08569768269144225</v>
+        <v>-0.08569768269144223</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04390299932943915</v>
+        <v>0.04390299932943926</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5273443083831006</v>
+        <v>0.5273443083831022</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2170,13 +2170,13 @@
         <v>0.04156356015237646</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08345569950857891</v>
+        <v>0.08345569950857894</v>
       </c>
       <c r="E30" t="n">
         <v>0.2463818614444229</v>
       </c>
       <c r="F30" t="n">
-        <v>7.251803917655306e-05</v>
+        <v>7.251803917655267e-05</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0003075021880133965</v>
+        <v>-0.0009348710380374935</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001577975195373548</v>
+        <v>0.001524420641947568</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.002785272363416314</v>
+        <v>-0.003922680593544156</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003400276739443106</v>
+        <v>0.002052938517469169</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8454936479856276</v>
+        <v>0.539702340552497</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.00502505014835909</v>
+        <v>0.0003075021880133949</v>
       </c>
       <c r="C32" t="n">
-        <v>0.004874127084529502</v>
+        <v>0.001577975195373549</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.01457816369010813</v>
+        <v>-0.002785272363416315</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00452806339338995</v>
+        <v>0.003400276739443106</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3025576450633091</v>
+        <v>0.8454936479856285</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001708340746372335</v>
+        <v>-0.00502505014835906</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001878385285250507</v>
+        <v>0.004874127084529532</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.001973226761808655</v>
+        <v>-0.01457816369010816</v>
       </c>
       <c r="E33" t="n">
-        <v>0.005389908254553325</v>
+        <v>0.004528063393390037</v>
       </c>
       <c r="F33" t="n">
-        <v>0.363100490744399</v>
+        <v>0.3025576450633151</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_stay_intention</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5041410727634079</v>
+        <v>0.00170834074637234</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01058339471591291</v>
+        <v>0.001878385285250503</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4833980002860471</v>
+        <v>-0.001973226761808642</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5248841452407688</v>
+        <v>0.005389908254553323</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.3631004907443967</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_stay_intention</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0009348710380374927</v>
+        <v>0.5041410727634079</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001524420641947569</v>
+        <v>0.01058339471591298</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003922680593544156</v>
+        <v>0.483398000286047</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002052938517469171</v>
+        <v>0.5248841452407689</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5397023405524974</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.311972303453005</v>
+        <v>-2.311972303453004</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4732783246148659</v>
+        <v>0.4732783246148637</v>
       </c>
       <c r="D2" t="n">
-        <v>1.034203273396138e-06</v>
+        <v>1.03420327339603e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04551110187272242</v>
+        <v>0.04551110187272237</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1066588120848096</v>
+        <v>0.1066588120848095</v>
       </c>
       <c r="D3" t="n">
         <v>0.6695993069686225</v>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3379756403631604</v>
+        <v>0.3379756403631605</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2250061856375072</v>
+        <v>0.2250061856375073</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1330783441003292</v>
+        <v>0.1330783441003293</v>
       </c>
     </row>
     <row r="5">
@@ -2401,10 +2401,10 @@
         <v>0.7569423399975517</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1751825039177965</v>
+        <v>0.1751825039177966</v>
       </c>
       <c r="D5" t="n">
-        <v>1.554091312807703e-05</v>
+        <v>1.554091312807723e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1782979025018587</v>
+        <v>-0.178297902501859</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2139495124929733</v>
+        <v>0.2139495124929734</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4046392581704369</v>
+        <v>0.4046392581704367</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.132443511774364</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1957468650864859</v>
+        <v>0.1957468650864858</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4986559440829725</v>
+        <v>0.4986559440829723</v>
       </c>
     </row>
     <row r="8">
@@ -2449,10 +2449,10 @@
         <v>-0.1002795981239172</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2109626858449117</v>
+        <v>0.2109626858449119</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6345426427644083</v>
+        <v>0.6345426427644085</v>
       </c>
     </row>
     <row r="9">
@@ -2468,7 +2468,7 @@
         <v>0.1702870574680672</v>
       </c>
       <c r="D9" t="n">
-        <v>3.663801651005724e-10</v>
+        <v>3.663801651005764e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09586471036369515</v>
+        <v>0.09586471036369429</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2812173938528693</v>
+        <v>0.2812173938528684</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7331850199863945</v>
+        <v>0.733185019986396</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2122047502073614</v>
+        <v>0.2122047502073606</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2718252954752363</v>
+        <v>0.2718252954752353</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4349989971387482</v>
+        <v>0.4349989971387483</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.248492190255086</v>
+        <v>-0.2484921902550868</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3060987030278327</v>
+        <v>0.3060987030278318</v>
       </c>
       <c r="D12" t="n">
-        <v>0.416904033845264</v>
+        <v>0.4169040338452613</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2437854598997692</v>
+        <v>0.2437854598997682</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2704267081993212</v>
+        <v>0.2704267081993213</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3673308223411915</v>
+        <v>0.3673308223411934</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2842899840705435</v>
+        <v>0.2842899840705426</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2794856252667396</v>
+        <v>0.2794856252667379</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3090630507092585</v>
+        <v>0.309063050709257</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.333863197227915</v>
+        <v>0.3338631972279141</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2681101141809201</v>
+        <v>0.2681101141809198</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2130411328890857</v>
+        <v>0.2130411328890862</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1317571536941386</v>
+        <v>0.1317571536941376</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2673158885530352</v>
+        <v>0.2673158885530345</v>
       </c>
       <c r="D16" t="n">
-        <v>0.622090775056322</v>
+        <v>0.6220907750563236</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1844896530482681</v>
+        <v>0.1844896530482672</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2747626237647856</v>
+        <v>0.2747626237647859</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5019332310651607</v>
+        <v>0.5019332310651632</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3852564364825101</v>
+        <v>0.3852564364825091</v>
       </c>
       <c r="C18" t="n">
         <v>0.2669629296237338</v>
       </c>
       <c r="D18" t="n">
-        <v>0.148989947720206</v>
+        <v>0.148989947720207</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1200201443966434</v>
+        <v>0.1200201443966426</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2768807649837055</v>
+        <v>0.2768807649837048</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6646716792835098</v>
+        <v>0.6646716792835113</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2300598125936615</v>
+        <v>0.2300598125936606</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2775759544090421</v>
+        <v>0.2775759544090414</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4072076759951918</v>
+        <v>0.4072076759951923</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2342426053793927</v>
+        <v>0.2342426053793918</v>
       </c>
       <c r="C21" t="n">
-        <v>0.267003539556027</v>
+        <v>0.2670035395560252</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3803228984925937</v>
+        <v>0.3803228984925923</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05070181680458596</v>
+        <v>0.05070181680458499</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2840939570184816</v>
+        <v>0.2840939570184809</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8583550727769782</v>
+        <v>0.8583550727769804</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02430178705992777</v>
+        <v>-0.02430178705992871</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2924104581161873</v>
+        <v>0.292410458116186</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9337652875979711</v>
+        <v>0.9337652875979682</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8776184811038454</v>
+        <v>0.8776184811038453</v>
       </c>
       <c r="C24" t="n">
         <v>0.1599092102015625</v>
       </c>
       <c r="D24" t="n">
-        <v>4.059818549219417e-08</v>
+        <v>4.059818549219492e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.590737345763946</v>
+        <v>-0.5907373457639462</v>
       </c>
       <c r="C25" t="n">
         <v>0.1168564510740924</v>
       </c>
       <c r="D25" t="n">
-        <v>4.298510219720117e-07</v>
+        <v>4.29851021972006e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1361198304387315</v>
+        <v>-0.1361198304387317</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1510147053221712</v>
+        <v>0.1510147053221714</v>
       </c>
       <c r="D26" t="n">
         <v>0.367392663145822</v>
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08678617737012831</v>
+        <v>-0.08678617737012842</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1575342766575602</v>
+        <v>0.1575342766575603</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5816998585693116</v>
+        <v>0.5816998585693114</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1139606954578559</v>
+        <v>-0.1139606954578562</v>
       </c>
       <c r="C28" t="n">
         <v>0.1481495337187114</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4417582678121278</v>
+        <v>0.4417582678121267</v>
       </c>
     </row>
     <row r="29">
@@ -2782,93 +2782,93 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3245032826079785</v>
+        <v>-0.3245032826079786</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1548576672030224</v>
+        <v>0.1548576672030222</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03612711839340743</v>
+        <v>0.03612711839340724</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002475297398078273</v>
+        <v>0.01479082094440969</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007264566116904072</v>
+        <v>0.007105685200950057</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7333025214094717</v>
+        <v>0.03738382522429076</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01826323504513888</v>
+        <v>0.002475297398078275</v>
       </c>
       <c r="C31" t="n">
-        <v>0.02286473001622312</v>
+        <v>0.007264566116904059</v>
       </c>
       <c r="D31" t="n">
-        <v>0.424434577820925</v>
+        <v>0.7333025214094711</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01275185748468731</v>
+        <v>0.01826323504513883</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008156254301674703</v>
+        <v>0.02286473001622316</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1179478912840566</v>
+        <v>0.4244345778209273</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_stay_intention</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.08169978351679094</v>
+        <v>-0.01275185748468729</v>
       </c>
       <c r="C33" t="n">
-        <v>0.05131576460014457</v>
+        <v>0.008156254301674418</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1113624354438364</v>
+        <v>0.1179478912840442</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_stay_intention</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01479082094440968</v>
+        <v>-0.08169978351679096</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007105685200950059</v>
+        <v>0.05131576460014454</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03738382522429085</v>
+        <v>0.1113624354438361</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.015</v>
+        <v>-0.392</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.034</v>
+        <v>-0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.019</v>
+        <v>0.362</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.001</v>
+        <v>-0.181</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.011</v>
+        <v>0.012</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.009999999999999998</v>
+        <v>0.169</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.013</v>
+        <v>0.059</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004999999999999999</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.351</v>
+        <v>-0.007</v>
       </c>
       <c r="D9" t="n">
-        <v>0.019</v>
+        <v>-0.021</v>
       </c>
       <c r="E9" t="n">
-        <v>0.332</v>
+        <v>-0.014</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.185</v>
+        <v>-0.215</v>
       </c>
       <c r="D10" t="n">
-        <v>0.011</v>
+        <v>-0.058</v>
       </c>
       <c r="E10" t="n">
-        <v>0.174</v>
+        <v>0.157</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.007</v>
+        <v>-0.015</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.021</v>
+        <v>-0.034</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.014</v>
+        <v>-0.019</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.181</v>
+        <v>-0.054</v>
       </c>
       <c r="D12" t="n">
-        <v>0.012</v>
+        <v>-0.024</v>
       </c>
       <c r="E12" t="n">
-        <v>0.169</v>
+        <v>0.03</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.054</v>
+        <v>0.036</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.024</v>
+        <v>-0.002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03</v>
+        <v>0.034</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.392</v>
+        <v>-0.001</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.03</v>
+        <v>-0.011</v>
       </c>
       <c r="E14" t="n">
-        <v>0.362</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.007</v>
+        <v>0.033</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.003</v>
+        <v>0.026</v>
       </c>
       <c r="E15" t="n">
-        <v>0.004</v>
+        <v>0.007000000000000003</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.036</v>
+        <v>-0.001</v>
       </c>
       <c r="D16" t="n">
         <v>-0.002</v>
       </c>
       <c r="E16" t="n">
-        <v>0.034</v>
+        <v>-0.001</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.368</v>
+        <v>0.013</v>
       </c>
       <c r="D17" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.361</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.059</v>
+        <v>0.01</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03899999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.215</v>
+        <v>0.014</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.058</v>
+        <v>0.018</v>
       </c>
       <c r="E19" t="n">
-        <v>0.157</v>
+        <v>-0.003999999999999998</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.044</v>
+        <v>-0.095</v>
       </c>
       <c r="D20" t="n">
-        <v>0.027</v>
+        <v>0.004</v>
       </c>
       <c r="E20" t="n">
-        <v>0.017</v>
+        <v>0.091</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.008</v>
+        <v>0.368</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.011</v>
+        <v>0.007</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.361</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>-0.096</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.076</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.074</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.095</v>
+        <v>-0.012</v>
       </c>
       <c r="D23" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="E23" t="n">
-        <v>0.091</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.019</v>
+        <v>-0.09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008</v>
+        <v>-0.031</v>
       </c>
       <c r="E24" t="n">
-        <v>0.011</v>
+        <v>0.059</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.096</v>
+        <v>-0.008</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02</v>
+        <v>-0.011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.076</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01</v>
+        <v>-0.019</v>
       </c>
       <c r="D26" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.075</v>
+        <v>0.351</v>
       </c>
       <c r="D28" t="n">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.332</v>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.014</v>
+        <v>0.075</v>
       </c>
       <c r="D29" t="n">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.003999999999999998</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="D30" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="E30" t="n">
-        <v>0.007000000000000003</v>
+        <v>0.017</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.012</v>
+        <v>0.185</v>
       </c>
       <c r="D31" t="n">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="E31" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.09</v>
+        <v>0.076</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.031</v>
+        <v>-0.002</v>
       </c>
       <c r="E32" t="n">
-        <v>0.059</v>
+        <v>0.074</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1388,7 +1388,7 @@
         <v>6217</v>
       </c>
       <c r="B2" t="n">
-        <v>6055.992193006092</v>
+        <v>6055.992193006093</v>
       </c>
       <c r="C2" t="n">
         <v>0.9952102075693736</v>
@@ -1397,13 +1397,13 @@
         <v>0.1622858171513957</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858932286536429</v>
+        <v>1.858932286536428</v>
       </c>
       <c r="F2" t="n">
         <v>1.152192362074074</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85789031706322</v>
+        <v>1.857890317063219</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.353573802712666</v>
+        <v>1.353573802712667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.111781623043566</v>
+        <v>0.1117816230435667</v>
       </c>
       <c r="D2" t="n">
-        <v>1.134485847413844</v>
+        <v>1.134485847413843</v>
       </c>
       <c r="E2" t="n">
-        <v>1.572661758011489</v>
+        <v>1.57266175801149</v>
       </c>
       <c r="F2" t="n">
-        <v>9.453643549727489e-34</v>
+        <v>9.453643549735873e-34</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01684973934795501</v>
+        <v>0.01684973934795502</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02218339938737489</v>
+        <v>0.02218339938737487</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02662892450596768</v>
+        <v>-0.02662892450596764</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06032840320187769</v>
+        <v>0.06032840320187767</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4475144961087134</v>
+        <v>0.4475144961087127</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004680048186736475</v>
+        <v>0.004680048186736477</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05214567125446189</v>
+        <v>0.05214567125446188</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0975235894216744</v>
+        <v>-0.09752358942167438</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1068836857951474</v>
+        <v>0.1068836857951473</v>
       </c>
       <c r="F4" t="n">
         <v>0.9284862752865164</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01802753319671222</v>
+        <v>-0.01802753319671224</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0351059918050009</v>
+        <v>0.03510599180500088</v>
       </c>
       <c r="D5" t="n">
         <v>-0.08683401277607225</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05077894638264781</v>
+        <v>0.05077894638264777</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6075895309376511</v>
+        <v>0.6075895309376507</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1567,16 +1567,16 @@
         <v>0.04751148647331695</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03543442571134348</v>
+        <v>0.03543442571134345</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.02193871173377634</v>
+        <v>-0.02193871173377631</v>
       </c>
       <c r="E6" t="n">
         <v>0.1169616846804102</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1799761535400185</v>
+        <v>0.1799761535400182</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.02470344421341204</v>
+        <v>-0.02470344421341206</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03375913660148893</v>
+        <v>0.03375913660148891</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09087013610149827</v>
+        <v>-0.09087013610149824</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04146324767467419</v>
+        <v>0.04146324767467413</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4643176277928899</v>
+        <v>0.4643176277928891</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01925751157934904</v>
+        <v>0.019257511579349</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03249460700462262</v>
+        <v>0.03249460700462261</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04443074784149426</v>
+        <v>-0.04443074784149427</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08294577100019235</v>
+        <v>0.08294577100019228</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5534240052549215</v>
+        <v>0.5534240052549222</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1648,10 +1648,10 @@
         <v>-0.1117164276674549</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0216393783840553</v>
+        <v>0.02163937838405532</v>
       </c>
       <c r="F9" t="n">
-        <v>0.185541187998942</v>
+        <v>0.1855411879989421</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1667,16 +1667,16 @@
         <v>0.108006405204335</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05860207996072134</v>
+        <v>0.0586020799607214</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.006851560937815207</v>
+        <v>-0.006851560937815346</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2228643713464853</v>
+        <v>0.2228643713464854</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06532210486217095</v>
+        <v>0.06532210486217126</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.002155543931905654</v>
+        <v>-0.002155543931905784</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06002430441707515</v>
+        <v>0.06002430441707516</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1198010187864414</v>
+        <v>-0.1198010187864416</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1154899309226301</v>
+        <v>0.11548993092263</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9713531768625314</v>
+        <v>0.9713531768625296</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1382027330165259</v>
+        <v>0.1382027330165258</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05978746914895721</v>
+        <v>0.05978746914895731</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02102144675777018</v>
+        <v>0.02102144675776989</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2553840192752816</v>
+        <v>0.2553840192752817</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02080156404096272</v>
+        <v>0.02080156404096305</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1224061847775766</v>
+        <v>0.1224061847775765</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05763612293239087</v>
+        <v>0.05763612293239093</v>
       </c>
       <c r="D13" t="n">
-        <v>0.009441459621567422</v>
+        <v>0.009441459621567228</v>
       </c>
       <c r="E13" t="n">
         <v>0.2353709099335858</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03368892209436414</v>
+        <v>0.03368892209436445</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.01605948332440321</v>
+        <v>-0.01605948332440315</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05643770073365873</v>
+        <v>0.05643770073365884</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1266753441326241</v>
+        <v>-0.1266753441326242</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09455637748381771</v>
+        <v>0.09455637748381794</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7759870816563198</v>
+        <v>0.7759870816563209</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1035989698740269</v>
+        <v>0.1035989698740268</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06028797128686297</v>
+        <v>0.06028797128686296</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0145632825492094</v>
+        <v>-0.01456328254920947</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2217612222972632</v>
+        <v>0.2217612222972631</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08572331750029806</v>
+        <v>0.08572331750029824</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02083305428097073</v>
+        <v>0.02083305428097068</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0565237990208397</v>
+        <v>0.05652379902083968</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.08995155606925545</v>
+        <v>-0.08995155606925546</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1316176646311969</v>
+        <v>0.1316176646311968</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7124472356899143</v>
+        <v>0.7124472356899147</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08702475870816757</v>
+        <v>0.08702475870816749</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05638348369484424</v>
+        <v>0.05638348369484428</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02348483865662852</v>
+        <v>-0.02348483865662868</v>
       </c>
       <c r="E17" t="n">
         <v>0.1975343560729637</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1227230457706391</v>
+        <v>0.1227230457706397</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.04234015284045959</v>
+        <v>0.0423401528404596</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05979849830098842</v>
+        <v>0.05979849830098848</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.07486275015905733</v>
+        <v>-0.07486275015905744</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1595430558399765</v>
+        <v>0.1595430558399766</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4789160136810118</v>
+        <v>0.4789160136810122</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06739003077305372</v>
+        <v>0.06739003077305364</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05810774114365023</v>
+        <v>0.05810774114365021</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.04649904909147702</v>
+        <v>-0.04649904909147708</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1812791106375845</v>
+        <v>0.1812791106375843</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2461535643763876</v>
+        <v>0.246153564376388</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.001531808616490251</v>
+        <v>-0.00153180861649036</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05617720975068351</v>
+        <v>0.05617720975068347</v>
       </c>
       <c r="D20" t="n">
         <v>-0.1116371164797823</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1085734992468018</v>
+        <v>0.1085734992468016</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9782464274556042</v>
+        <v>0.9782464274556025</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09669367936441987</v>
+        <v>0.09669367936441978</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0591417298393631</v>
+        <v>0.05914172983936323</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.01922198110412965</v>
+        <v>-0.01922198110412998</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2126093398329694</v>
+        <v>0.2126093398329695</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1020598551750289</v>
+        <v>0.10205985517503</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04161731869983512</v>
+        <v>0.04161731869983511</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05891200060017089</v>
+        <v>0.05891200060017098</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07384808073370187</v>
+        <v>-0.07384808073370205</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1570827181333721</v>
+        <v>0.1570827181333723</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4799195657238088</v>
+        <v>0.4799195657238094</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.08357026518461759</v>
+        <v>0.08357026518461749</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05655202274398948</v>
+        <v>0.05655202274398949</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.02726966264649179</v>
+        <v>-0.0272696626464919</v>
       </c>
       <c r="E23" t="n">
-        <v>0.194410193015727</v>
+        <v>0.1944101930157269</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1394722742661427</v>
+        <v>0.1394722742661432</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.06180044074249916</v>
+        <v>-0.06180044074249914</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0500916027818642</v>
+        <v>0.05009160278186423</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1599781781228394</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03637729663784106</v>
+        <v>0.03637729663784112</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2172966281742635</v>
+        <v>0.2172966281742638</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.009821945543911271</v>
+        <v>0.009821945543911317</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02791990290120034</v>
+        <v>0.02791990290120041</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04490005859429677</v>
+        <v>-0.04490005859429685</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06454394968211931</v>
+        <v>0.06454394968211949</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7249956806795027</v>
+        <v>0.724995680679502</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.007141328148584081</v>
+        <v>0.007141328148583986</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03367730708489818</v>
+        <v>0.03367730708489817</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05886498083411194</v>
+        <v>-0.05886498083411202</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0731476371312801</v>
+        <v>0.07314763713127999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8320667485145375</v>
+        <v>0.8320667485145398</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04372637637293082</v>
+        <v>-0.04372637637293078</v>
       </c>
       <c r="C27" t="n">
         <v>0.03548652400230914</v>
@@ -2098,10 +2098,10 @@
         <v>-0.1132786853539729</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02582593260811127</v>
+        <v>0.02582593260811132</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2178756304376085</v>
+        <v>0.217875630437609</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05468422483154232</v>
+        <v>-0.05468422483154229</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03444153292457986</v>
+        <v>0.03444153292457983</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1221883889360693</v>
+        <v>-0.1221883889360692</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01281993927298469</v>
+        <v>0.01281993927298464</v>
       </c>
       <c r="F28" t="n">
-        <v>0.112344977518535</v>
+        <v>0.1123449775185348</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02089734168100154</v>
+        <v>-0.0208973416810015</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03306200599683337</v>
+        <v>0.03306200599683336</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08569768269144225</v>
+        <v>-0.08569768269144218</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04390299932943915</v>
+        <v>0.04390299932943918</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5273443083831009</v>
+        <v>0.5273443083831015</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1649187804765008</v>
+        <v>0.1649187804765009</v>
       </c>
       <c r="C30" t="n">
         <v>0.04156356015237647</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0834556995085788</v>
+        <v>0.08345569950857895</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2463818614444228</v>
+        <v>0.2463818614444229</v>
       </c>
       <c r="F30" t="n">
-        <v>7.251803917655401e-05</v>
+        <v>7.251803917655267e-05</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0003075021880133968</v>
+        <v>0.0003075021880133948</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001577975195373545</v>
+        <v>0.001577975195373544</v>
       </c>
       <c r="D31" t="n">
         <v>-0.002785272363416308</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003400276739443101</v>
+        <v>0.003400276739443097</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8454936479856272</v>
+        <v>0.8454936479856281</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001708340746372339</v>
+        <v>0.001708340746372333</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00187838528525056</v>
+        <v>0.001878385285250502</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.001973226761808754</v>
+        <v>-0.001973226761808646</v>
       </c>
       <c r="E32" t="n">
-        <v>0.005389908254553433</v>
+        <v>0.005389908254553313</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3631004907444114</v>
+        <v>0.3631004907443982</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_stay_intention</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.005025050148359062</v>
+        <v>0.5041410727634079</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004874127084529506</v>
+        <v>0.01058339471591286</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01457816369010811</v>
+        <v>0.4833980002860472</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004528063393389985</v>
+        <v>0.5248841452407687</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3025576450633123</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_stay_intention</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5041410727634079</v>
+        <v>-0.005025050148359063</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01058339471591284</v>
+        <v>0.00487412708452948</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4833980002860472</v>
+        <v>-0.01457816369010806</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5248841452407687</v>
+        <v>0.004528063393389934</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.3025576450633096</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0009348710380374943</v>
+        <v>-0.0009348710380374933</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001524420641947566</v>
+        <v>0.001524420641947569</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003922680593544154</v>
+        <v>-0.003922680593544157</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002052938517469165</v>
+        <v>0.002052938517469171</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5397023405524961</v>
+        <v>0.5397023405524972</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.311972303453005</v>
+        <v>-2.311972303453007</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4732783246148577</v>
+        <v>0.4732783246148621</v>
       </c>
       <c r="D2" t="n">
-        <v>1.034203273395692e-06</v>
+        <v>1.034203273395907e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04551110187272239</v>
+        <v>0.0455111018727225</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1066588120848096</v>
+        <v>0.1066588120848095</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6695993069686226</v>
+        <v>0.6695993069686219</v>
       </c>
     </row>
     <row r="4">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3379756403631604</v>
+        <v>0.3379756403631605</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2250061856375073</v>
+        <v>0.2250061856375074</v>
       </c>
       <c r="D4" t="n">
         <v>0.1330783441003295</v>
@@ -2401,10 +2401,10 @@
         <v>0.7569423399975517</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1751825039177967</v>
+        <v>0.1751825039177966</v>
       </c>
       <c r="D5" t="n">
-        <v>1.554091312807735e-05</v>
+        <v>1.554091312807712e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.178297902501859</v>
+        <v>-0.1782979025018588</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2139495124929733</v>
+        <v>0.2139495124929734</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4046392581704363</v>
+        <v>0.4046392581704369</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.132443511774364</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1957468650864859</v>
+        <v>0.1957468650864858</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4986559440829724</v>
+        <v>0.4986559440829723</v>
       </c>
     </row>
     <row r="8">
@@ -2452,7 +2452,7 @@
         <v>0.2109626858449118</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6345426427644082</v>
+        <v>0.6345426427644083</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.067311062636429</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1702870574680673</v>
+        <v>0.1702870574680672</v>
       </c>
       <c r="D9" t="n">
-        <v>3.663801651005818e-10</v>
+        <v>3.663801651005724e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09586471036369462</v>
+        <v>0.09586471036369534</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2812173938528694</v>
+        <v>0.2812173938528698</v>
       </c>
       <c r="D10" t="n">
-        <v>0.733185019986396</v>
+        <v>0.7331850199863944</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2122047502073611</v>
+        <v>0.2122047502073616</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2718252954752361</v>
+        <v>0.2718252954752365</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4349989971387486</v>
+        <v>0.4349989971387483</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2484921902550863</v>
+        <v>-0.248492190255086</v>
       </c>
       <c r="C12" t="n">
-        <v>0.306098703027832</v>
+        <v>0.3060987030278322</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4169040338452623</v>
+        <v>0.4169040338452634</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2437854598997688</v>
+        <v>0.2437854598997692</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2704267081993214</v>
+        <v>0.2704267081993223</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3673308223411924</v>
+        <v>0.3673308223411934</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2842899840705428</v>
+        <v>0.2842899840705435</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2794856252667393</v>
+        <v>0.2794856252667392</v>
       </c>
       <c r="D14" t="n">
-        <v>0.309063050709259</v>
+        <v>0.3090630507092578</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3338631972279147</v>
+        <v>0.333863197227915</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2681101141809203</v>
+        <v>0.2681101141809207</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2130411328890863</v>
+        <v>0.2130411328890865</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1317571536941383</v>
+        <v>0.1317571536941387</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2673158885530355</v>
+        <v>0.2673158885530354</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6220907750563232</v>
+        <v>0.622090775056322</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1844896530482677</v>
+        <v>0.1844896530482681</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2747626237647861</v>
+        <v>0.2747626237647864</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5019332310651623</v>
+        <v>0.5019332310651619</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3852564364825097</v>
+        <v>0.3852564364825101</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2669629296237339</v>
+        <v>0.2669629296237346</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1489899477202066</v>
+        <v>0.1489899477202071</v>
       </c>
     </row>
     <row r="19">
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.120020144396643</v>
+        <v>0.1200201443966434</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2768807649837055</v>
+        <v>0.2768807649837066</v>
       </c>
       <c r="D19" t="n">
         <v>0.664671679283511</v>
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.230059812593661</v>
+        <v>0.2300598125936614</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2775759544090419</v>
+        <v>0.2775759544090424</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4072076759951924</v>
+        <v>0.4072076759951923</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2342426053793921</v>
+        <v>0.2342426053793929</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2670035395560267</v>
+        <v>0.2670035395560269</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3803228984925944</v>
+        <v>0.3803228984925932</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0507018168045855</v>
+        <v>0.05070181680458598</v>
       </c>
       <c r="C22" t="n">
         <v>0.2840939570184813</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8583550727769793</v>
+        <v>0.858355072776978</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02430178705992826</v>
+        <v>-0.02430178705992777</v>
       </c>
       <c r="C23" t="n">
-        <v>0.292410458116187</v>
+        <v>0.2924104581161884</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9337652875979696</v>
+        <v>0.9337652875979713</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8776184811038453</v>
+        <v>0.8776184811038454</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1599092102015625</v>
+        <v>0.1599092102015624</v>
       </c>
       <c r="D24" t="n">
-        <v>4.059818549219462e-08</v>
+        <v>4.059818549219388e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5907373457639463</v>
+        <v>-0.590737345763946</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1168564510740925</v>
+        <v>0.1168564510740924</v>
       </c>
       <c r="D25" t="n">
-        <v>4.298510219720156e-07</v>
+        <v>4.298510219720117e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1361198304387314</v>
+        <v>-0.1361198304387317</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1510147053221715</v>
+        <v>0.1510147053221713</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3673926631458232</v>
+        <v>0.3673926631458218</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08678617737012827</v>
+        <v>-0.08678617737012843</v>
       </c>
       <c r="C27" t="n">
         <v>0.1575342766575605</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5816998585693125</v>
+        <v>0.5816998585693116</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1139606954578559</v>
+        <v>-0.1139606954578561</v>
       </c>
       <c r="C28" t="n">
         <v>0.1481495337187116</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4417582678121285</v>
+        <v>0.4417582678121279</v>
       </c>
     </row>
     <row r="29">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3245032826079783</v>
+        <v>-0.3245032826079786</v>
       </c>
       <c r="C29" t="n">
         <v>0.1548576672030224</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03612711839340765</v>
+        <v>0.03612711839340742</v>
       </c>
     </row>
     <row r="30">
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002475297398078279</v>
+        <v>0.002475297398078278</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007264566116904048</v>
+        <v>0.007264566116904079</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7333025214094703</v>
+        <v>0.7333025214094715</v>
       </c>
     </row>
     <row r="31">
@@ -2814,45 +2814,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0127518574846873</v>
+        <v>-0.01275185748468727</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008156254301674297</v>
+        <v>0.008156254301674579</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1179478912840384</v>
+        <v>0.117947891284052</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_stay_intention</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01826323504513886</v>
+        <v>-0.0816997835167909</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02286473001622345</v>
+        <v>0.05131576460014481</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4244345778209324</v>
+        <v>0.1113624354438382</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_stay_intention</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.08169978351679091</v>
+        <v>0.01826323504513893</v>
       </c>
       <c r="C33" t="n">
-        <v>0.051315764600145</v>
+        <v>0.02286473001622346</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1113624354438396</v>
+        <v>0.4244345778209309</v>
       </c>
     </row>
     <row r="34">
@@ -2865,10 +2865,10 @@
         <v>0.01479082094440969</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007105685200950063</v>
+        <v>0.007105685200950046</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03738382522429089</v>
+        <v>0.03738382522429044</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.181</v>
+        <v>-0.392</v>
       </c>
       <c r="D6" t="n">
-        <v>0.012</v>
+        <v>-0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>0.169</v>
+        <v>0.362</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01</v>
+        <v>-0.181</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006</v>
+        <v>0.169</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.076</v>
+        <v>0.044</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.002</v>
+        <v>0.027</v>
       </c>
       <c r="E8" t="n">
-        <v>0.074</v>
+        <v>0.017</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.095</v>
+        <v>0.351</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="E9" t="n">
-        <v>0.091</v>
+        <v>0.332</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.008</v>
+        <v>0.014</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.011</v>
+        <v>0.018</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.002999999999999999</v>
+        <v>-0.003999999999999998</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.392</v>
+        <v>-0.095</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03</v>
+        <v>0.004</v>
       </c>
       <c r="E11" t="n">
-        <v>0.362</v>
+        <v>0.091</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.001</v>
+        <v>-0.215</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.002</v>
+        <v>-0.058</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.001</v>
+        <v>0.157</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="D13" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.003999999999999998</v>
+        <v>0.006</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.059</v>
+        <v>0.076</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>-0.002</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03899999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.033</v>
+        <v>0.368</v>
       </c>
       <c r="D15" t="n">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007000000000000003</v>
+        <v>0.361</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.007</v>
+        <v>-0.001</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E16" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.036</v>
+        <v>-0.001</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.002</v>
+        <v>-0.011</v>
       </c>
       <c r="E17" t="n">
-        <v>0.034</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.015</v>
+        <v>0.013</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.034</v>
+        <v>0.008</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.019</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.096</v>
+        <v>0.007</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02</v>
+        <v>-0.003</v>
       </c>
       <c r="E19" t="n">
-        <v>0.076</v>
+        <v>0.004</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.001</v>
+        <v>-0.054</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.011</v>
+        <v>-0.024</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.009999999999999998</v>
+        <v>0.03</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.021</v>
+        <v>-0.011</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.014</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.075</v>
+        <v>0.185</v>
       </c>
       <c r="D22" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.019</v>
+        <v>0.059</v>
       </c>
       <c r="D23" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="E23" t="n">
-        <v>0.011</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.351</v>
+        <v>-0.09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.019</v>
+        <v>-0.031</v>
       </c>
       <c r="E24" t="n">
-        <v>0.332</v>
+        <v>0.059</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.033</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.024</v>
+        <v>0.026</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03</v>
+        <v>0.007000000000000003</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.09</v>
+        <v>0.036</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.031</v>
+        <v>-0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.059</v>
+        <v>0.034</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.368</v>
+        <v>0.075</v>
       </c>
       <c r="D28" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="E28" t="n">
-        <v>0.361</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.013</v>
+        <v>-0.019</v>
       </c>
       <c r="D29" t="n">
         <v>0.008</v>
       </c>
       <c r="E29" t="n">
-        <v>0.004999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.215</v>
+        <v>-0.015</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.058</v>
+        <v>-0.034</v>
       </c>
       <c r="E30" t="n">
-        <v>0.157</v>
+        <v>-0.019</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.185</v>
+        <v>-0.096</v>
       </c>
       <c r="D31" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="E31" t="n">
-        <v>0.174</v>
+        <v>0.076</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.044</v>
+        <v>-0.007</v>
       </c>
       <c r="D32" t="n">
-        <v>0.027</v>
+        <v>-0.021</v>
       </c>
       <c r="E32" t="n">
-        <v>0.017</v>
+        <v>-0.014</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>

--- a/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.024</v>
+        <v>-0.082</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001</v>
+        <v>-0.028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.023</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.369</v>
+        <v>0.045</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="E7" t="n">
-        <v>0.359</v>
+        <v>0.039</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.388</v>
+        <v>-0.008</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.033</v>
+        <v>-0.014</v>
       </c>
       <c r="E8" t="n">
-        <v>0.355</v>
+        <v>-0.006</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003</v>
+        <v>-0.031</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.001</v>
+        <v>0.028</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.036</v>
+        <v>-0.117</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007</v>
+        <v>-0.005</v>
       </c>
       <c r="E10" t="n">
-        <v>0.029</v>
+        <v>0.112</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.095</v>
+        <v>0.19</v>
       </c>
       <c r="D11" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="E11" t="n">
-        <v>0.077</v>
+        <v>0.171</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.008</v>
+        <v>-0.183</v>
       </c>
       <c r="D12" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002</v>
+        <v>0.173</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.082</v>
+        <v>0.011</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.028</v>
+        <v>0.005</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.005999999999999999</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="D14" t="n">
-        <v>0.023</v>
+        <v>0.007</v>
       </c>
       <c r="E14" t="n">
-        <v>0.012</v>
+        <v>0.029</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.183</v>
+        <v>0.003</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E15" t="n">
-        <v>0.173</v>
+        <v>-0.001</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.216</v>
+        <v>0.075</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.061</v>
+        <v>0.006</v>
       </c>
       <c r="E16" t="n">
-        <v>0.155</v>
+        <v>0.06899999999999999</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.011</v>
+        <v>-0.018</v>
       </c>
       <c r="D17" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.005999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.015</v>
+        <v>0.015</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.001</v>
+        <v>0.021</v>
       </c>
       <c r="E18" t="n">
-        <v>0.014</v>
+        <v>-0.006000000000000002</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.015</v>
+        <v>0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.028</v>
+        <v>0.006</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.013</v>
+        <v>0.002</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.117</v>
+        <v>0.35</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.005</v>
+        <v>0.021</v>
       </c>
       <c r="E20" t="n">
-        <v>0.112</v>
+        <v>0.329</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.045</v>
+        <v>0.369</v>
       </c>
       <c r="D21" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>0.039</v>
+        <v>0.359</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.031</v>
+        <v>-0.388</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.003</v>
+        <v>-0.033</v>
       </c>
       <c r="E23" t="n">
-        <v>0.028</v>
+        <v>0.355</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.075</v>
+        <v>-0.015</v>
       </c>
       <c r="D24" t="n">
-        <v>0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06899999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.008</v>
+        <v>-0.216</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.014</v>
+        <v>-0.061</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.006</v>
+        <v>0.155</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.099</v>
+        <v>0.024</v>
       </c>
       <c r="D26" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.091</v>
+        <v>0.023</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="D27" t="n">
-        <v>0.004</v>
+        <v>0.023</v>
       </c>
       <c r="E27" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.19</v>
+        <v>0.036</v>
       </c>
       <c r="D28" t="n">
         <v>0.019</v>
       </c>
       <c r="E28" t="n">
-        <v>0.171</v>
+        <v>0.017</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="E29" t="n">
-        <v>0.014</v>
+        <v>-0.013</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.35</v>
+        <v>0.099</v>
       </c>
       <c r="D30" t="n">
-        <v>0.021</v>
+        <v>0.008</v>
       </c>
       <c r="E30" t="n">
-        <v>0.329</v>
+        <v>0.091</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.015</v>
+        <v>-0.095</v>
       </c>
       <c r="D31" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.006000000000000002</v>
+        <v>0.077</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.036</v>
+        <v>0.02</v>
       </c>
       <c r="D32" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="E32" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1394,16 +1394,16 @@
         <v>0.9947743467572683</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1660928874117529</v>
+        <v>0.1660928874117528</v>
       </c>
       <c r="E2" t="n">
-        <v>1.865027655308433</v>
+        <v>1.865027655308432</v>
       </c>
       <c r="F2" t="n">
         <v>1.171427247069243</v>
       </c>
       <c r="G2" t="n">
-        <v>1.864596865244262</v>
+        <v>1.864596865244261</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.275822258384234</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1069470810900246</v>
+        <v>0.1069470810900279</v>
       </c>
       <c r="D2" t="n">
-        <v>1.066209831196101</v>
+        <v>1.066209831196094</v>
       </c>
       <c r="E2" t="n">
-        <v>1.485434685572367</v>
+        <v>1.485434685572373</v>
       </c>
       <c r="F2" t="n">
-        <v>8.309842829360053e-33</v>
+        <v>8.309842829396915e-33</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01800447850586531</v>
+        <v>0.01800447850586529</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0213507398033405</v>
+        <v>0.02135073980334051</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02384220255196786</v>
+        <v>-0.0238422025519679</v>
       </c>
       <c r="E3" t="n">
         <v>0.05985115956369848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3990764054904832</v>
+        <v>0.3990764054904838</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02991188913162587</v>
+        <v>0.02991188913162584</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05176670956335588</v>
+        <v>0.05176670956335589</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.07154899721069685</v>
+        <v>-0.07154899721069691</v>
       </c>
       <c r="E4" t="n">
         <v>0.1313727754739486</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5633850117014995</v>
+        <v>0.5633850117014999</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1542,16 +1542,16 @@
         <v>-0.0154720502216834</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03553090787611782</v>
+        <v>0.03553090787611791</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08511134999688487</v>
+        <v>-0.08511134999688505</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05416724955351808</v>
+        <v>0.05416724955351824</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6632334471021618</v>
+        <v>0.6632334471021626</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0504179349047237</v>
+        <v>0.05041793490472377</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03745187675104911</v>
+        <v>0.03745187675104917</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.02298639468076552</v>
+        <v>-0.02298639468076557</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1238222644902129</v>
+        <v>0.1238222644902131</v>
       </c>
       <c r="F6" t="n">
         <v>0.1782361447451596</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.02931525280736767</v>
+        <v>-0.02931525280736764</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03582274952505803</v>
+        <v>0.03582274952505809</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09952655170368073</v>
+        <v>-0.09952655170368083</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04089604608894538</v>
+        <v>0.04089604608894554</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4131620525635831</v>
+        <v>0.4131620525635843</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01644171178981753</v>
+        <v>0.01644171178981751</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03477296636371701</v>
+        <v>0.03477296636371709</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.05171204991869054</v>
+        <v>-0.05171204991869072</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08459547349832559</v>
+        <v>0.08459547349832575</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6363342616632277</v>
+        <v>0.6363342616632288</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1642,16 +1642,16 @@
         <v>-0.05527943239633056</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03735234252485594</v>
+        <v>0.037352342524856</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1284886784832521</v>
+        <v>-0.1284886784832522</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01792981369059098</v>
+        <v>0.01792981369059111</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1388877833970801</v>
+        <v>0.1388877833970807</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09605882417873421</v>
+        <v>0.09605882417873399</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05742666981735252</v>
+        <v>0.05742666981735275</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.01649538041535009</v>
+        <v>-0.01649538041535077</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2086130287728185</v>
+        <v>0.2086130287728187</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09438213845083422</v>
+        <v>0.09438213845083633</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.001065366777801385</v>
+        <v>-0.001065366777801343</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0588450476706301</v>
+        <v>0.05884504767063036</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.116399540880779</v>
+        <v>-0.1163995408807795</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1142688073251762</v>
+        <v>0.1142688073251768</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9855553984186013</v>
+        <v>0.9855553984186018</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1717,16 +1717,16 @@
         <v>0.1215296229167752</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06051266181143794</v>
+        <v>0.06051266181143827</v>
       </c>
       <c r="D12" t="n">
-        <v>0.002926985157704509</v>
+        <v>0.002926985157703857</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2401322606758458</v>
+        <v>0.2401322606758465</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04460783441964934</v>
+        <v>0.04460783441965051</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1742,16 +1742,16 @@
         <v>0.1155105893049998</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05822105252646868</v>
+        <v>0.05822105252646895</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00139942321110649</v>
+        <v>0.001399423211105894</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2296217553988931</v>
+        <v>0.2296217553988937</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04725579954469874</v>
+        <v>0.04725579954469986</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.01349104366052399</v>
+        <v>-0.01349104366052391</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05800285674031262</v>
+        <v>0.05800285674031284</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.127174553871973</v>
+        <v>-0.1271745538719734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1001924665509251</v>
+        <v>0.1001924665509256</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8160776615643248</v>
+        <v>0.8160776615643266</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1023769247116161</v>
+        <v>0.102376924711616</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0595235459617378</v>
+        <v>0.05952354596173808</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0142870816055046</v>
+        <v>-0.01428708160550518</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2190409310287367</v>
+        <v>0.2190409310287373</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08544335753096526</v>
+        <v>0.08544335753096684</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02773007216127393</v>
+        <v>0.02773007216127385</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05575403142349979</v>
+        <v>0.05575403142350013</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.08154582142170011</v>
+        <v>-0.08154582142170085</v>
       </c>
       <c r="E16" t="n">
-        <v>0.137005965744248</v>
+        <v>0.1370059657442486</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6189320829370111</v>
+        <v>0.6189320829370142</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08146773835430325</v>
+        <v>0.08146773835430321</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05882847756163694</v>
+        <v>0.05882847756163705</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.03383395893182783</v>
+        <v>-0.0338339589318281</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1967694356404343</v>
+        <v>0.1967694356404345</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1661029072269727</v>
+        <v>0.1661029072269737</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.04222495509270444</v>
+        <v>0.04222495509270457</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05926643319079038</v>
+        <v>0.05926643319079065</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.07393511945339398</v>
+        <v>-0.07393511945339437</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1583850296388029</v>
+        <v>0.1583850296388035</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4761800550547723</v>
+        <v>0.476180055054773</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05036461608296308</v>
+        <v>0.0503646160829631</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05647297747030942</v>
+        <v>0.0564729774703098</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.06032038585858528</v>
+        <v>-0.060320385858586</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1610496180245115</v>
+        <v>0.1610496180245122</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3724810158898639</v>
+        <v>0.372481015889867</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.002269094079180349</v>
+        <v>-0.002269094079180408</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05478509344621922</v>
+        <v>0.05478509344621961</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1096459041234314</v>
+        <v>-0.1096459041234322</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1051077159650707</v>
+        <v>0.1051077159650714</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9669625892804233</v>
+        <v>0.9669625892804228</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1942,16 +1942,16 @@
         <v>0.1011722893565771</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05887376870338964</v>
+        <v>0.05887376870338989</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.01421817693620801</v>
+        <v>-0.01421817693620851</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2165627556493622</v>
+        <v>0.2165627556493626</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08571251909863616</v>
+        <v>0.08571251909863752</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04125942965104785</v>
+        <v>0.04125942965104787</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05865032202135233</v>
+        <v>0.05865032202135254</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07369308919247913</v>
+        <v>-0.07369308919247952</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1562119484945748</v>
+        <v>0.1562119484945753</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4817555923149472</v>
+        <v>0.4817555923149486</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.07996355752818142</v>
+        <v>0.07996355752818143</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05607097622505462</v>
+        <v>0.05607097622505489</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.02993353645092728</v>
+        <v>-0.02993353645092779</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1898606515072901</v>
+        <v>0.1898606515072906</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1538356784345921</v>
+        <v>0.1538356784345939</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.05962925925699782</v>
+        <v>-0.0596292592569977</v>
       </c>
       <c r="C24" t="n">
         <v>0.04902929854742429</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1557249185972114</v>
+        <v>-0.1557249185972113</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03646640008321578</v>
+        <v>0.03646640008321589</v>
       </c>
       <c r="F24" t="n">
-        <v>0.223910092487158</v>
+        <v>0.2239100924871592</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01279378886562625</v>
+        <v>0.01279378886562634</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02808380584485919</v>
+        <v>0.02808380584485917</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04224945913911322</v>
+        <v>-0.0422494591391131</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06783703687036573</v>
+        <v>0.06783703687036578</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6487081982201406</v>
+        <v>0.6487081982201381</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.001052356458934201</v>
+        <v>-0.001052356458934058</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03394016399758235</v>
+        <v>0.03394016399758241</v>
       </c>
       <c r="D26" t="n">
         <v>-0.06757385552357859</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06546914260571018</v>
+        <v>0.06546914260571046</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9752645729383022</v>
+        <v>0.9752645729383056</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.05150620611606125</v>
+        <v>-0.05150620611606122</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03536756561086329</v>
+        <v>0.03536756561086334</v>
       </c>
       <c r="D27" t="n">
         <v>-0.1208253609342107</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01781294870208817</v>
+        <v>0.01781294870208828</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1453064217190537</v>
+        <v>0.1453064217190544</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05686604124806978</v>
+        <v>-0.05686604124806975</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03396525249488084</v>
+        <v>0.0339652524948809</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1234367128638454</v>
+        <v>-0.1234367128638455</v>
       </c>
       <c r="E28" t="n">
-        <v>0.009704630367705885</v>
+        <v>0.009704630367706038</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09408311194579937</v>
+        <v>0.09408311194580014</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01909808526182823</v>
+        <v>-0.01909808526182822</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03372713011317744</v>
+        <v>0.0337271301131775</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08520204558555233</v>
+        <v>-0.08520204558555243</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04700587506189587</v>
+        <v>0.04700587506189598</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5712218730524306</v>
+        <v>0.5712218730524314</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2167,7 +2167,7 @@
         <v>0.1731458137302275</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04545217693888522</v>
+        <v>0.0454521769388852</v>
       </c>
       <c r="D30" t="n">
         <v>0.08406118391107047</v>
@@ -2176,7 +2176,7 @@
         <v>0.2622304435493845</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0001393008282982229</v>
+        <v>0.0001393008282982222</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_stay_intention</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.005666561332464264</v>
+        <v>0.5020195969910464</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00473206393571513</v>
+        <v>0.01149836474635207</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.003608113554078252</v>
+        <v>0.4794832162070913</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01494123621900678</v>
+        <v>0.5245559777750014</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2311187437090179</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2217,16 +2217,16 @@
         <v>0.002001845221445705</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001850472688462888</v>
+        <v>0.001850472688462894</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.001625014602316564</v>
+        <v>-0.001625014602316574</v>
       </c>
       <c r="E32" t="n">
-        <v>0.005628705045207974</v>
+        <v>0.005628705045207984</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2793404778383842</v>
+        <v>0.2793404778383858</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0003348762717462531</v>
+        <v>-0.001111955599069821</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001546510604345189</v>
+        <v>0.001506841016546479</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003365981357972097</v>
+        <v>-0.004065309721928644</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002696228814479591</v>
+        <v>0.001841398523789002</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8285694368357257</v>
+        <v>0.4605519835428297</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001111955599069822</v>
+        <v>-0.0003348762717462553</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001506841016546482</v>
+        <v>0.001546510604345188</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00406530972192865</v>
+        <v>-0.003365981357972097</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001841398523789006</v>
+        <v>0.002696228814479587</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4605519835428301</v>
+        <v>0.8285694368357244</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>baseline_stay_intention</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5020195969910464</v>
+        <v>0.005666561332464269</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01149836474635203</v>
+        <v>0.00473206393571513</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4794832162070914</v>
+        <v>-0.003608113554078247</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5245559777750014</v>
+        <v>0.01494123621900679</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.2311187437090173</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.044402994661898</v>
+        <v>-2.0444029946619</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4821469351514772</v>
+        <v>0.4821469351514817</v>
       </c>
       <c r="D2" t="n">
-        <v>2.233133729989092e-05</v>
+        <v>2.23313372998945e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01505455408376913</v>
+        <v>0.01505455408376917</v>
       </c>
       <c r="C3" t="n">
         <v>0.1069076273853754</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8880134581894009</v>
+        <v>0.8880134581894007</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3198990752681581</v>
+        <v>0.319899075268158</v>
       </c>
       <c r="C4" t="n">
         <v>0.2290795329845115</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1625777642877017</v>
+        <v>0.162577764287702</v>
       </c>
     </row>
     <row r="5">
@@ -2401,10 +2401,10 @@
         <v>0.7750347446848579</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1688211614555384</v>
+        <v>0.1688211614555382</v>
       </c>
       <c r="D5" t="n">
-        <v>4.414180109307259e-06</v>
+        <v>4.414180109307153e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2433,10 +2433,10 @@
         <v>0.1366657028780133</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1831371214342475</v>
+        <v>0.1831371214342473</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4555176426168609</v>
+        <v>0.4555176426168605</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09889028967509492</v>
+        <v>-0.09889028967509486</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1946078480717117</v>
+        <v>0.1946078480717115</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6113470295356542</v>
+        <v>0.6113470295356539</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.069110771975244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1650737230649844</v>
+        <v>0.1650737230649842</v>
       </c>
       <c r="D9" t="n">
-        <v>9.383392319101072e-11</v>
+        <v>9.383392319100696e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1119009615186509</v>
+        <v>0.111900961518651</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2824211731858493</v>
+        <v>0.2824211731858489</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6919426226088764</v>
+        <v>0.6919426226088756</v>
       </c>
     </row>
     <row r="11">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2611236352610811</v>
+        <v>0.2611236352610812</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2774733931431559</v>
+        <v>0.2774733931431561</v>
       </c>
       <c r="D11" t="n">
         <v>0.3466657578376419</v>
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1939089526843256</v>
+        <v>-0.1939089526843254</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3055476547763329</v>
+        <v>0.3055476547763328</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5256713703270238</v>
+        <v>0.5256713703270239</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3065393878616868</v>
+        <v>0.3065393878616869</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2738506295758543</v>
+        <v>0.2738506295758542</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2629835562447594</v>
+        <v>0.2629835562447592</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2638760119996927</v>
+        <v>0.2638760119996929</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2613995276525051</v>
+        <v>0.261399527652505</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3127473918380141</v>
+        <v>0.3127473918380134</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2956601583182392</v>
+        <v>0.2956601583182394</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2677539904188883</v>
+        <v>0.2677539904188884</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2694963440025971</v>
+        <v>0.2694963440025969</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1386905919251779</v>
+        <v>0.1386905919251782</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2550466518843216</v>
+        <v>0.2550466518843207</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5865893017194252</v>
+        <v>0.5865893017194233</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1938409199355756</v>
+        <v>0.1938409199355758</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2730966488449671</v>
+        <v>0.2730966488449667</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4778351670889263</v>
+        <v>0.477835167088925</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4815743968506268</v>
+        <v>0.4815743968506269</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2529416624505248</v>
+        <v>0.252941662450524</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05692384476977456</v>
+        <v>0.05692384476977374</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1149788961200541</v>
+        <v>0.1149788961200543</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2793217700241809</v>
+        <v>0.2793217700241811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.680606240897758</v>
+        <v>0.6806062408977578</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.255673267282099</v>
+        <v>0.2556732672820991</v>
       </c>
       <c r="C20" t="n">
         <v>0.279769936132808</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3607853172601301</v>
+        <v>0.3607853172601297</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2545331291659194</v>
+        <v>0.2545331291659195</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2758468790509387</v>
+        <v>0.2758468790509381</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3561461544708144</v>
+        <v>0.3561461544708132</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006271850142108592</v>
+        <v>0.006271850142108709</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2915848725191328</v>
+        <v>0.291584872519132</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9828392107405722</v>
+        <v>0.9828392107405718</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.08280881647945568</v>
+        <v>-0.08280881647945539</v>
       </c>
       <c r="C23" t="n">
         <v>0.2917349721836066</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7765257434050186</v>
+        <v>0.7765257434050192</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8945118574943137</v>
+        <v>0.8945118574943136</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1582066454520368</v>
+        <v>0.1582066454520367</v>
       </c>
       <c r="D24" t="n">
-        <v>1.566899849547347e-08</v>
+        <v>1.566899849547307e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5749322739631791</v>
+        <v>-0.5749322739631793</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158508654576946</v>
+        <v>0.1158508654576945</v>
       </c>
       <c r="D25" t="n">
-        <v>6.952244164617642e-07</v>
+        <v>6.952244164617352e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1463885426628081</v>
+        <v>-0.146388542662808</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1535320349609192</v>
+        <v>0.1535320349609193</v>
       </c>
       <c r="D26" t="n">
-        <v>0.340350823887394</v>
+        <v>0.3403508238873945</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.09212591454782337</v>
+        <v>-0.09212591454782341</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1508931321561187</v>
+        <v>0.1508931321561188</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5415058151077937</v>
+        <v>0.5415058151077939</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05794622808295304</v>
+        <v>-0.05794622808295293</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1546011259971958</v>
+        <v>0.1546011259971956</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7078009104396236</v>
+        <v>0.7078009104396237</v>
       </c>
     </row>
     <row r="29">
@@ -2788,23 +2788,23 @@
         <v>0.1612787800554736</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0206757912706018</v>
+        <v>0.02067579127060177</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_stay_intention</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01750392325086382</v>
+        <v>-0.08329329099132557</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02278206436922979</v>
+        <v>0.05100747069355982</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4422968984845819</v>
+        <v>0.1024768667997012</v>
       </c>
     </row>
     <row r="31">
@@ -2814,61 +2814,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01267461279025099</v>
+        <v>-0.01267461279025094</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008406160112485236</v>
+        <v>0.008406160112485031</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1316116741217152</v>
+        <v>0.131611674121707</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.007135237646216833</v>
+        <v>0.01393310830996258</v>
       </c>
       <c r="C32" t="n">
-        <v>0.006300306504041696</v>
+        <v>0.006906314450377999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2574149122249705</v>
+        <v>0.04364911402196035</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01393310830996259</v>
+        <v>0.007135237646216832</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006906314450377983</v>
+        <v>0.0063003065040417</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04364911402195966</v>
+        <v>0.2574149122249709</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_stay_intention</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.08329329099132562</v>
+        <v>-0.01750392325086376</v>
       </c>
       <c r="C34" t="n">
-        <v>0.05100747069355983</v>
+        <v>0.02278206436922979</v>
       </c>
       <c r="D34" t="n">
-        <v>0.102476866799701</v>
+        <v>0.4422968984845834</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_stay_intention_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.095</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.018</v>
+        <v>-0.032</v>
       </c>
       <c r="E6" t="n">
-        <v>0.077</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02</v>
+        <v>-0.095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.016</v>
+        <v>0.077</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.024</v>
+        <v>0.369</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>0.023</v>
+        <v>0.359</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.216</v>
+        <v>-0.183</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.061</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>0.155</v>
+        <v>0.173</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.008</v>
+        <v>0.02</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.014</v>
+        <v>0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.006</v>
+        <v>0.016</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.082</v>
+        <v>0.015</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.028</v>
+        <v>0.021</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05400000000000001</v>
+        <v>-0.006000000000000002</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.117</v>
+        <v>0.008</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E13" t="n">
-        <v>0.112</v>
+        <v>0.002</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.015</v>
+        <v>-0.216</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.001</v>
+        <v>-0.061</v>
       </c>
       <c r="E14" t="n">
-        <v>0.014</v>
+        <v>0.155</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.015</v>
+        <v>0.35</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.028</v>
+        <v>0.021</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.013</v>
+        <v>0.329</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.031</v>
+        <v>-0.082</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.003</v>
+        <v>-0.028</v>
       </c>
       <c r="E16" t="n">
-        <v>0.028</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.035</v>
+        <v>-0.117</v>
       </c>
       <c r="D17" t="n">
-        <v>0.023</v>
+        <v>-0.005</v>
       </c>
       <c r="E17" t="n">
-        <v>0.012</v>
+        <v>0.112</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="D18" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002</v>
+        <v>0.005999999999999999</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.099</v>
+        <v>0.19</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008</v>
+        <v>0.019</v>
       </c>
       <c r="E19" t="n">
-        <v>0.091</v>
+        <v>0.171</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.35</v>
+        <v>0.024</v>
       </c>
       <c r="D20" t="n">
-        <v>0.021</v>
+        <v>0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.329</v>
+        <v>0.023</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.036</v>
+        <v>0.099</v>
       </c>
       <c r="D21" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="E21" t="n">
-        <v>0.029</v>
+        <v>0.091</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.045</v>
+        <v>-0.008</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006</v>
+        <v>-0.014</v>
       </c>
       <c r="E22" t="n">
-        <v>0.039</v>
+        <v>-0.006</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.183</v>
+        <v>-0.018</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="E24" t="n">
-        <v>0.173</v>
+        <v>0.014</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.032</v>
+        <v>-0.003</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03899999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.369</v>
+        <v>0.003</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E26" t="n">
-        <v>0.359</v>
+        <v>-0.001</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.011</v>
+        <v>0.035</v>
       </c>
       <c r="D27" t="n">
-        <v>0.005</v>
+        <v>0.023</v>
       </c>
       <c r="E27" t="n">
-        <v>0.005999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.003</v>
+        <v>-0.015</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.001</v>
+        <v>0.014</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.015</v>
+        <v>0.036</v>
       </c>
       <c r="D29" t="n">
-        <v>0.021</v>
+        <v>0.007</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.006000000000000002</v>
+        <v>0.029</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.018</v>
+        <v>0.045</v>
       </c>
       <c r="D30" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E30" t="n">
-        <v>0.014</v>
+        <v>0.039</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.19</v>
+        <v>-0.015</v>
       </c>
       <c r="D31" t="n">
-        <v>0.019</v>
+        <v>-0.028</v>
       </c>
       <c r="E31" t="n">
-        <v>0.171</v>
+        <v>-0.013</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1467,16 +1467,16 @@
         <v>1.275822258384234</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1069470810900255</v>
+        <v>0.1069470810900239</v>
       </c>
       <c r="D2" t="n">
-        <v>1.066209831196099</v>
+        <v>1.066209831196102</v>
       </c>
       <c r="E2" t="n">
-        <v>1.485434685572369</v>
+        <v>1.485434685572365</v>
       </c>
       <c r="F2" t="n">
-        <v>8.309842829369327e-33</v>
+        <v>8.309842829352326e-33</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0180044785058653</v>
+        <v>0.01800447850586532</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0213507398033405</v>
+        <v>0.02135073980334051</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02384220255196788</v>
+        <v>-0.02384220255196787</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05985115956369848</v>
+        <v>0.05985115956369851</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3990764054904834</v>
+        <v>0.3990764054904831</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02991188913162589</v>
+        <v>0.02991188913162586</v>
       </c>
       <c r="C4" t="n">
         <v>0.05176670956335588</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.07154899721069682</v>
+        <v>-0.07154899721069685</v>
       </c>
       <c r="E4" t="n">
         <v>0.1313727754739486</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5633850117014991</v>
+        <v>0.5633850117014996</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01547205022168342</v>
+        <v>-0.01547205022168339</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03553090787611783</v>
+        <v>0.03553090787611787</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08511134999688491</v>
+        <v>-0.08511134999688495</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05416724955351807</v>
+        <v>0.05416724955351817</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6632334471021615</v>
+        <v>0.6632334471021624</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05041793490472365</v>
+        <v>0.05041793490472366</v>
       </c>
       <c r="C6" t="n">
         <v>0.03745187675104913</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.02931525280736768</v>
+        <v>-0.02931525280736764</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03582274952505803</v>
+        <v>0.03582274952505805</v>
       </c>
       <c r="D7" t="n">
         <v>-0.09952655170368074</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0408960460889454</v>
+        <v>0.04089604608894546</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4131620525635831</v>
+        <v>0.4131620525635838</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01644171178981749</v>
+        <v>0.0164417117898175</v>
       </c>
       <c r="C8" t="n">
         <v>0.03477296636371704</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.05171204991869065</v>
+        <v>-0.05171204991869063</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08459547349832562</v>
+        <v>0.08459547349832564</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6363342616632288</v>
+        <v>0.6363342616632286</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.05527943239633059</v>
+        <v>-0.05527943239633055</v>
       </c>
       <c r="C9" t="n">
         <v>0.03735234252485595</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1284886784832522</v>
+        <v>-0.1284886784832521</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01792981369059098</v>
+        <v>0.01792981369059102</v>
       </c>
       <c r="F9" t="n">
-        <v>0.13888778339708</v>
+        <v>0.1388877833970803</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09605882417873404</v>
+        <v>0.096058824178734</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05742666981735264</v>
+        <v>0.0574266698173526</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.01649538041535049</v>
+        <v>-0.01649538041535047</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2086130287728186</v>
+        <v>0.2086130287728185</v>
       </c>
       <c r="F10" t="n">
         <v>0.09438213845083541</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.001065366777801402</v>
+        <v>-0.001065366777801433</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05884504767063009</v>
+        <v>0.05884504767063008</v>
       </c>
       <c r="D11" t="n">
         <v>-0.116399540880779</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1142688073251762</v>
+        <v>0.1142688073251761</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9855553984186011</v>
+        <v>0.9855553984186006</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1215296229167751</v>
+        <v>0.1215296229167752</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06051266181143811</v>
+        <v>0.06051266181143809</v>
       </c>
       <c r="D12" t="n">
-        <v>0.002926985157704107</v>
+        <v>0.002926985157704204</v>
       </c>
       <c r="E12" t="n">
         <v>0.2401322606758461</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04460783441965003</v>
+        <v>0.0446078344196499</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1742,16 +1742,16 @@
         <v>0.1155105893049998</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0582210525264688</v>
+        <v>0.05822105252646877</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001399423211106185</v>
+        <v>0.001399423211106254</v>
       </c>
       <c r="E13" t="n">
         <v>0.2296217553988933</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04725579954469933</v>
+        <v>0.04725579954469918</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.01349104366052393</v>
+        <v>-0.01349104366052394</v>
       </c>
       <c r="C14" t="n">
         <v>0.05800285674031273</v>
@@ -1776,7 +1776,7 @@
         <v>0.1001924665509253</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8160776615643259</v>
+        <v>0.8160776615643257</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1792,16 +1792,16 @@
         <v>0.102376924711616</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05952354596173792</v>
+        <v>0.0595235459617379</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.01428708160550486</v>
+        <v>-0.01428708160550483</v>
       </c>
       <c r="E15" t="n">
         <v>0.2190409310287369</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08544335753096599</v>
+        <v>0.08544335753096596</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02773007216127383</v>
+        <v>0.02773007216127384</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05575403142350004</v>
+        <v>0.05575403142349994</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.08154582142170069</v>
+        <v>-0.08154582142170048</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1370059657442484</v>
+        <v>0.1370059657442482</v>
       </c>
       <c r="F16" t="n">
-        <v>0.618932082937014</v>
+        <v>0.6189320829370131</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08146773835430315</v>
+        <v>0.08146773835430318</v>
       </c>
       <c r="C17" t="n">
-        <v>0.058828477561637</v>
+        <v>0.05882847756163697</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.03383395893182807</v>
+        <v>-0.03383395893182797</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1967694356404344</v>
+        <v>0.1967694356404343</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1661029072269737</v>
+        <v>0.1661029072269733</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.04222495509270442</v>
+        <v>0.04222495509270435</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05926643319079043</v>
+        <v>0.05926643319079036</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.07393511945339409</v>
+        <v>-0.07393511945339402</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1583850296388029</v>
+        <v>0.1583850296388027</v>
       </c>
       <c r="F18" t="n">
-        <v>0.476180055054773</v>
+        <v>0.4761800550547731</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05036461608296305</v>
+        <v>0.05036461608296306</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0564729774703096</v>
+        <v>0.05647297747030948</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.06032038585858567</v>
+        <v>-0.06032038585858541</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1610496180245118</v>
+        <v>0.1610496180245115</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3724810158898657</v>
+        <v>0.3724810158898646</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.002269094079180475</v>
+        <v>-0.002269094079180524</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0547850934462194</v>
+        <v>0.05478509344621932</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1096459041234319</v>
+        <v>-0.1096459041234317</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1051077159650709</v>
+        <v>0.1051077159650707</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9669625892804217</v>
+        <v>0.9669625892804209</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1011722893565771</v>
+        <v>0.101172289356577</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05887376870338972</v>
+        <v>0.0588737687033896</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.01421817693620819</v>
+        <v>-0.01421817693620797</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2165627556493623</v>
+        <v>0.2165627556493621</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08571251909863659</v>
+        <v>0.08571251909863596</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0412594296510478</v>
+        <v>0.04125942965104781</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05865032202135251</v>
+        <v>0.05865032202135247</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07369308919247954</v>
+        <v>-0.07369308919247944</v>
       </c>
       <c r="E22" t="n">
         <v>0.1562119484945751</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4817555923149491</v>
+        <v>0.4817555923149487</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.07996355752818138</v>
+        <v>0.07996355752818142</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05607097622505478</v>
+        <v>0.05607097622505471</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.02993353645092763</v>
+        <v>-0.02993353645092746</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1898606515072904</v>
+        <v>0.1898606515072903</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1538356784345934</v>
+        <v>0.1538356784345927</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.05962925925699777</v>
+        <v>-0.05962925925699775</v>
       </c>
       <c r="C24" t="n">
         <v>0.04902929854742429</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1557249185972114</v>
+        <v>-0.1557249185972113</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03646640008321582</v>
+        <v>0.03646640008321585</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2239100924871585</v>
+        <v>0.2239100924871588</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,16 +2039,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01279378886562633</v>
+        <v>0.01279378886562632</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02808380584485915</v>
+        <v>0.02808380584485914</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04224945913911307</v>
+        <v>-0.04224945913911306</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06783703687036574</v>
+        <v>0.0678370368703657</v>
       </c>
       <c r="F25" t="n">
         <v>0.6487081982201381</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.001052356458934115</v>
+        <v>-0.001052356458933983</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03394016399758239</v>
+        <v>0.03394016399758241</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0675738555235786</v>
+        <v>-0.0675738555235785</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06546914260571036</v>
+        <v>0.06546914260571055</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9752645729383042</v>
+        <v>0.9752645729383073</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.05150620611606128</v>
+        <v>-0.0515062061160612</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03536756561086332</v>
+        <v>0.03536756561086329</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1208253609342108</v>
+        <v>-0.1208253609342106</v>
       </c>
       <c r="E27" t="n">
         <v>0.0178129487020882</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1453064217190538</v>
+        <v>0.1453064217190539</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,16 +2114,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05686604124806974</v>
+        <v>-0.0568660412480697</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03396525249488087</v>
+        <v>0.03396525249488084</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1234367128638455</v>
+        <v>-0.1234367128638454</v>
       </c>
       <c r="E28" t="n">
-        <v>0.009704630367705976</v>
+        <v>0.009704630367705969</v>
       </c>
       <c r="F28" t="n">
         <v>0.09408311194579982</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01909808526182825</v>
+        <v>-0.01909808526182817</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03372713011317747</v>
+        <v>0.03372713011317743</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08520204558555242</v>
+        <v>-0.08520204558555225</v>
       </c>
       <c r="E29" t="n">
         <v>0.04700587506189591</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5712218730524306</v>
+        <v>0.5712218730524317</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2167,16 +2167,16 @@
         <v>0.1731458137302275</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0454521769388852</v>
+        <v>0.04545217693888521</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08406118391107047</v>
+        <v>0.08406118391107045</v>
       </c>
       <c r="E30" t="n">
         <v>0.2622304435493845</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0001393008282982222</v>
+        <v>0.0001393008282982229</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_stay_intention</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5020195969910464</v>
+        <v>-0.000334876271746253</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01149836474635205</v>
+        <v>0.00154651060434519</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4794832162070913</v>
+        <v>-0.003365981357972098</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5245559777750014</v>
+        <v>0.002696228814479592</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.8285694368357257</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.00111195559906982</v>
+        <v>0.005666561332464266</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00150684101654648</v>
+        <v>0.004732063935715113</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004065309721928645</v>
+        <v>-0.003608113554078218</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001841398523789004</v>
+        <v>0.01494123621900675</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4605519835428303</v>
+        <v>0.2311187437090159</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_stay_intention</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.005666561332464261</v>
+        <v>0.5020195969910464</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004732063935715109</v>
+        <v>0.01149836474635201</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003608113554078214</v>
+        <v>0.4794832162070914</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01494123621900674</v>
+        <v>0.5245559777750013</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2311187437090159</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.002001845221445704</v>
+        <v>0.002001845221445706</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001850472688462875</v>
+        <v>0.001850472688462907</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00162501460231654</v>
+        <v>-0.001625014602316599</v>
       </c>
       <c r="E34" t="n">
-        <v>0.005628705045207947</v>
+        <v>0.00562870504520801</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2793404778383813</v>
+        <v>0.279340477838389</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0003348762717462548</v>
+        <v>-0.001111955599069821</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001546510604345189</v>
+        <v>0.00150684101654648</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003365981357972098</v>
+        <v>-0.004065309721928645</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002696228814479588</v>
+        <v>0.001841398523789003</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8285694368357247</v>
+        <v>0.46055198354283</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.044402994661898</v>
+        <v>-2.044402994661901</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4821469351514689</v>
+        <v>0.4821469351514793</v>
       </c>
       <c r="D2" t="n">
-        <v>2.233133729988362e-05</v>
+        <v>2.233133729989217e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01505455408376903</v>
+        <v>0.01505455408376909</v>
       </c>
       <c r="C3" t="n">
         <v>0.1069076273853753</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8880134581894017</v>
+        <v>0.8880134581894013</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3198990752681579</v>
+        <v>0.3198990752681581</v>
       </c>
       <c r="C4" t="n">
         <v>0.2290795329845114</v>
       </c>
       <c r="D4" t="n">
-        <v>0.162577764287702</v>
+        <v>0.1625777642877015</v>
       </c>
     </row>
     <row r="5">
@@ -2401,10 +2401,10 @@
         <v>0.7750347446848579</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1688211614555381</v>
+        <v>0.168821161455538</v>
       </c>
       <c r="D5" t="n">
-        <v>4.414180109307103e-06</v>
+        <v>4.414180109307005e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1781873720200714</v>
+        <v>-0.1781873720200713</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2078420070630832</v>
+        <v>0.2078420070630831</v>
       </c>
       <c r="D6" t="n">
         <v>0.391267360432746</v>
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1366657028780133</v>
+        <v>0.1366657028780134</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1831371214342472</v>
+        <v>0.183137121434247</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4555176426168603</v>
+        <v>0.4555176426168597</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09889028967509483</v>
+        <v>-0.0988902896750949</v>
       </c>
       <c r="C8" t="n">
         <v>0.1946078480717114</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6113470295356539</v>
+        <v>0.6113470295356537</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.069110771975244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1650737230649842</v>
+        <v>0.1650737230649841</v>
       </c>
       <c r="D9" t="n">
-        <v>9.383392319100696e-11</v>
+        <v>9.383392319100288e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1119009615186507</v>
+        <v>0.111900961518651</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2824211731858484</v>
+        <v>0.2824211731858479</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6919426226088761</v>
+        <v>0.6919426226088747</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2611236352610807</v>
+        <v>0.2611236352610808</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2774733931431552</v>
+        <v>0.2774733931431548</v>
       </c>
       <c r="D11" t="n">
-        <v>0.346665757837641</v>
+        <v>0.3466657578376401</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.193908952684326</v>
+        <v>-0.1939089526843258</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3055476547763317</v>
+        <v>0.3055476547763322</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5256713703270213</v>
+        <v>0.5256713703270224</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3065393878616864</v>
+        <v>0.3065393878616868</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2738506295758533</v>
+        <v>0.2738506295758535</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2629835562447583</v>
+        <v>0.2629835562447582</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2638760119996924</v>
+        <v>0.2638760119996926</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2613995276525046</v>
+        <v>0.2613995276525041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3127473918380136</v>
+        <v>0.3127473918380124</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2956601583182388</v>
+        <v>0.2956601583182391</v>
       </c>
       <c r="C15" t="n">
         <v>0.267753990418887</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2694963440025954</v>
+        <v>0.2694963440025949</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1386905919251777</v>
+        <v>0.138690591925178</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2550466518843207</v>
+        <v>0.2550466518843206</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5865893017194244</v>
+        <v>0.5865893017194235</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1938409199355753</v>
+        <v>0.1938409199355756</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2730966488449665</v>
+        <v>0.2730966488449662</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4778351670889258</v>
+        <v>0.4778351670889247</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4815743968506266</v>
+        <v>0.4815743968506269</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2529416624505236</v>
+        <v>0.2529416624505232</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05692384476977345</v>
+        <v>0.05692384476977295</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1149788961200538</v>
+        <v>0.1149788961200542</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2793217700241809</v>
+        <v>0.2793217700241808</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6806062408977588</v>
+        <v>0.6806062408977576</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2556732672820986</v>
+        <v>0.2556732672820989</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2797699361328074</v>
+        <v>0.2797699361328072</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3607853172601297</v>
+        <v>0.3607853172601287</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2545331291659191</v>
+        <v>0.2545331291659194</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2758468790509375</v>
+        <v>0.2758468790509369</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3561461544708128</v>
+        <v>0.3561461544708113</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006271850142108275</v>
+        <v>0.006271850142108427</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2915848725191315</v>
+        <v>0.2915848725191316</v>
       </c>
       <c r="D22" t="n">
-        <v>0.982839210740573</v>
+        <v>0.9828392107405726</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.08280881647945587</v>
+        <v>-0.08280881647945573</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2917349721836061</v>
+        <v>0.2917349721836059</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7765257434050177</v>
+        <v>0.7765257434050179</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8945118574943136</v>
+        <v>0.8945118574943137</v>
       </c>
       <c r="C24" t="n">
         <v>0.1582066454520367</v>
       </c>
       <c r="D24" t="n">
-        <v>1.566899849547307e-08</v>
+        <v>1.566899849547324e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5749322739631793</v>
+        <v>-0.5749322739631791</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158508654576945</v>
+        <v>0.1158508654576944</v>
       </c>
       <c r="D25" t="n">
-        <v>6.952244164617352e-07</v>
+        <v>6.952244164617259e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1463885426628079</v>
+        <v>-0.146388542662808</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1535320349609191</v>
+        <v>0.1535320349609193</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3403508238873941</v>
+        <v>0.3403508238873946</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.09212591454782337</v>
+        <v>-0.09212591454782325</v>
       </c>
       <c r="C27" t="n">
         <v>0.1508931321561187</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5415058151077936</v>
+        <v>0.5415058151077945</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.057946228082953</v>
+        <v>-0.05794622808295282</v>
       </c>
       <c r="C28" t="n">
         <v>0.1546011259971956</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7078009104396233</v>
+        <v>0.7078009104396242</v>
       </c>
     </row>
     <row r="29">
@@ -2782,61 +2782,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3731753764435959</v>
+        <v>-0.3731753764435958</v>
       </c>
       <c r="C29" t="n">
         <v>0.1612787800554736</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02067579127060177</v>
+        <v>0.02067579127060182</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baseline_stay_intention</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.08329329099132553</v>
+        <v>0.007135237646216843</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05100747069355983</v>
+        <v>0.006300306504041691</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1024768667997014</v>
+        <v>0.2574149122249695</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01393310830996259</v>
+        <v>-0.01750392325086375</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006906314450377992</v>
+        <v>0.02278206436922982</v>
       </c>
       <c r="D31" t="n">
-        <v>0.04364911402196003</v>
+        <v>0.4422968984845843</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_stay_intention</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01750392325086378</v>
+        <v>-0.08329329099132551</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02278206436922996</v>
+        <v>0.05100747069355976</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4422968984845863</v>
+        <v>0.1024768667997011</v>
       </c>
     </row>
     <row r="33">
@@ -2846,29 +2846,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01267461279025097</v>
+        <v>-0.01267461279025094</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008406160112485178</v>
+        <v>0.008406160112485286</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1316116741217131</v>
+        <v>0.1316116741217191</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.007135237646216838</v>
+        <v>0.0139331083099626</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006300306504041713</v>
+        <v>0.006906314450377973</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2574149122249716</v>
+        <v>0.04364911402195927</v>
       </c>
     </row>
   </sheetData>
